--- a/framework/fw_popsizes.xlsx
+++ b/framework/fw_popsizes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute-my.sharepoint.com/personal/chris_seaman_burnet_edu_au/Documents/Documents/GitRepos/burnet-hbv/framework/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{7D9B31DB-38E3-D74D-81CE-1D7B61EA513E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62E23F43-8C5B-402B-BF93-3CAD1902C788}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EBD0E1-238A-494E-8BD6-D92923C4E82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -3146,16 +3146,28 @@
     <t>Total Population Size</t>
   </si>
   <si>
-    <t>pop_arrive</t>
-  </si>
-  <si>
     <t>Total Arrivals by broad pop group</t>
   </si>
   <si>
-    <t>pop_depart</t>
+    <t>Total Departures by broad pop group</t>
   </si>
   <si>
-    <t>Total Departures by broad pop group</t>
+    <t>emig_rate</t>
+  </si>
+  <si>
+    <t>imig_rate</t>
+  </si>
+  <si>
+    <t>mig_rate</t>
+  </si>
+  <si>
+    <t>Rate of Migration (neg = emig)</t>
+  </si>
+  <si>
+    <t>max(mig_rate*sus, 0)</t>
+  </si>
+  <si>
+    <t>min(mig_rate, 0)*-1</t>
   </si>
 </sst>
 </file>
@@ -4036,7 +4048,8 @@
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:398" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -5665,7 +5678,7 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -8075,7 +8088,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="4" customWidth="1"/>
@@ -8169,14 +8182,12 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>54</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -8189,10 +8200,10 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>54</v>
@@ -8201,23 +8212,45 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="H4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>41</v>
       </c>
     </row>
